--- a/energy_costs_data_centre_economics.xlsx
+++ b/energy_costs_data_centre_economics.xlsx
@@ -7,12 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="US Electricity Prices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Europe Electricity Prices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="US vs Europe Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Data Centre Economics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Strategic Implications" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Oil Price Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hyperscaler Profiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Margin Impact Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scenario Deep Dive" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sensitivity &amp; Takeaways" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="US Electricity Prices" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Europe Electricity Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="US vs Europe Comparison" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data Centre Economics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Strategic Implications" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sources &amp; Methodology" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +63,19 @@
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +92,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF6"/>
+        <bgColor rgb="00DEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,6 +158,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,6 +537,5827 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas Price Scenarios and Electricity Cost Pass-Through</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>How oil prices flow through to data centre electricity costs in the US and Europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Brent Crude ($/bbl)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Henry Hub Gas ($/MMBtu)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>EU TTF Gas (€/MWh)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>US Elec. Industrial (¢/kWh)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>EU Elec. Industrial (¢/kWh)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>US vs Baseline</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>EU vs Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>HISTORICAL REFERENCE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2020 (COVID low)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>~14</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2021 (recovery)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>~21</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2022 (energy crisis)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>100.93</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>~32</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2023 (normalising)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>~21</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2024 (low gas)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>~18.7</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025 (current)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>~20-22</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FORWARD SCENARIOS</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>S1: Low Oil ($50/bbl)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>16-18</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>-18% to -23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>S2: Base Case ($70/bbl)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>20-22</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>S3: Moderate High ($90/bbl)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>24-27</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>+15% to +27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>S4: High ($110/bbl)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>30-35</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>+26%</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>+45% to +68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>S5: Crisis ($130/bbl)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>40-50</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>+45%</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>+90% to +140%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>S6: Extreme ($150/bbl)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>50-60</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>+63%</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>+140% to +190%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Gas-electricity pass-through: US ~40% of electricity from gas (direct price link). EU marginal pricing set by gas under merit order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>EU carbon cost (ETS at ~€70/t CO₂) adds €5-10/MWh on top of gas-driven wholesale prices. EU sensitivity to gas prices ~2-3x US.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Oil-to-gas link: Brent ↔ Henry Hub correlation ~0.5-0.7; Brent ↔ TTF correlation ~0.6-0.8 (higher due to LNG indexation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Scenarios assume proportional gas price pass-through. Actual outcomes depend on renewable mix, PPA coverage, and regional grid dynamics.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Strategic Implications: Energy Costs &amp; Data Centre Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>US Implications</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Europe Implications</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>LOCATION ECONOMICS</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Energy Cost Arbitrage</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>US industrial rates are 45-55% cheaper than EU average</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Strong pull for new DC investment; Virginia, Texas, Ohio dominate</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Risk of investment leakage to US; Nordics are the EU bright spot</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Intra-Regional Variation</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>5-10x price range within each region</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Oregon/Texas cheapest; California premium market</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Nordics cheapest; Ireland/Germany most expensive despite DC density</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Grid Availability</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Power access becoming binding constraint</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Some delays in Virginia; Texas grid more flexible</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>7-10 year grid connection waits in legacy hubs; Dublin/Amsterdam moratoriums</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DEMAND &amp; CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>AI-Driven Demand Surge</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>US DC demand forecast to double by 2030 (366→728 TWh)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Strongest 4-year electricity demand growth since 2000</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>150% EU DC demand growth expected 2024-2035</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Data Centres as % of Grid</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>US: ~9% of total; Dublin: ~80% of local demand</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Utilities investing heavily to serve DC load</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Grid saturation in key hubs forcing diversification</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Rack Density Escalation</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Average &lt;8 kW moving toward 30+ kW for AI racks</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Higher energy intensity per sqft amplifies cost differences</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Same trend, but with higher base electricity costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>COST MANAGEMENT STRATEGIES</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>PPA Adoption</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Corporates locking in long-term renewable contracts</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Solar PPAs rising +9% Y/Y due to demand; wind competitive in ERCOT</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>EU solar PPAs declining; Spain at €32.50/MWh is highly competitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>On-Site Generation</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Operators investing in behind-the-meter power</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Natural gas + solar co-generation; some nuclear SMR interest</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Wind/solar + battery; less gas flexibility due to carbon costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Efficiency Improvements</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>PUE stagnant at ~1.55 globally; hyperscalers at 1.10-1.20</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Marginal gains from liquid cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Nordics benefit from free cooling; reduces PUE to &lt;1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>INVESTMENT OUTLOOK</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Capital Flows</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>$3T infrastructure supercycle through 2030</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>US attracting disproportionate share due to energy + policy advantages</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>€86B foreign investment 2016-2024; but growth slowing vs US</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Hyperscaler Strategy</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Big Tech driving 50% of DC capex</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Concentrating in US; aggressive PPA + nuclear deals</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Expanding in Nordics/Spain; constrained in legacy hubs</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign Considerations</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Data sovereignty rules keep some workloads local</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Less of a factor domestically; drives some EU-to-US shift</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>GDPR + data localisation rules protect EU DC demand floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Emerging Market Competition</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Middle East, SE Asia offering cheap power + incentives</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>US still preferred for latency and connectivity</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>EU faces competition from Gulf states for non-latency-sensitive loads</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>KEY RISKS</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>US Energy Price Risk</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>AI-driven demand pushing US prices to record highs (17.14¢ all-sector avg early 2026)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Energy cost advantage may narrow if demand outpaces supply</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Could reduce the US-EU gap if US prices rise faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>EU Competitiveness Risk</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>EU wholesale prices ~2x US; carbon costs add €5-10/MWh</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Could accelerate US DC investment at EU's expense</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Need grid investment + renewable buildout to compete</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Carbon Regulation</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>EU ETS at €70/t CO₂; US has no comparable federal scheme</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Regulatory advantage for US operators; lower compliance costs</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Adds ~€5-10/MWh to EU electricity costs for fossil generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Analysis based on EIA, IEA, Eurostat, Uptime Institute, JLL, Dell'Oro, and LevelTen data as of Q4 2025 / early 2026.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A31:D31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data Sources &amp; Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Data Used</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>US Energy Information Administration (EIA)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>US retail &amp; wholesale electricity prices by sector and state</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2020-2025, monthly/annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>EIA Electric Power Monthly</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Industrial, commercial, residential rates; state-level breakdowns</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2020-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>EIA Wholesale Markets Portal</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Day-ahead and real-time hub prices (PJM, ERCOT, etc.)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2020-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>EU industrial electricity prices by country, incl. taxes &amp; levies</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>IEA Electricity 2026 Report</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>EU wholesale prices, demand forecasts, industrial comparisons</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2024-2025 + forecasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>IEA Electricity Mid-Year Update 2025</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>H1 2025 wholesale prices by country, year-on-year changes</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>H1 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ember Climate / Ember Energy</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>European wholesale day-ahead prices, renewables share data</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2020-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>CubeConsults</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>European industrial electricity price rankings by country (2024)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>LevelTen Energy PPA Price Index</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Solar &amp; wind PPA prices for North America and Europe (Q4 2025)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Uptime Institute Global DC Survey</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PUE trends, rack densities, sustainability metrics</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Lawrence Berkeley National Lab (LBNL)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>US data centre energy consumption analysis</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>JLL 2026 Global Data Center Outlook</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DC market capacity, investment cycles, infrastructure supercycle</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2024-2030 forecasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dell'Oro Group</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Data centre capex forecasts, GPU share of spending</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2024-2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Arizton Advisory</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Global DC market investment sizing</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2023-2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>US data centres and energy outlook</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>2025-2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Reuters / Financial Media</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>DC demand-driven electricity price records, policy developments</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>METHODOLOGY NOTES</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Currency Conversion</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EUR/USD at ~1.09 (2024-2025 average) used for cross-region comparisons</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Energy Cost Scenarios</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Annual cost = IT Load (MW) × PUE × 8,760 hrs × Rate ($/kWh)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Wholesale vs Retail</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>DCs negotiate rates between wholesale and retail; shown separately</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PPA Impact</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>PPAs can reduce effective rates 10-30% vs retail; growing in adoption</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Data Vintage</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Most data as of Q4 2025 or early 2026; some 2025 figures are estimates</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004472C4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hyperscale Cloud Vendor Profiles: Energy Exposure &amp; Margins</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Meta (infra)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Industry Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>REVENUE &amp; MARGINS</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Annual Cloud Revenue (2025E)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>$142B</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>$131B</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>$71B</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>N/A (infra cost)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>$25B</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Q3 2025 Operating Margin</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>~43%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>23.7%</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>~25%</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Full-Year 2024 Op. Margin</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>~37%</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>~42%</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>~20%</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>~22%</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Margin Trend</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Expanding</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Stable-high</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Rapidly expanding</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Expanding</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Annual Capex (2025E)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>~$85-100B</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>~$80B</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>~$75B</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>~$38-40B</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>~$16B</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ENERGY CONSUMPTION (ESTIMATED)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Total Electricity (2024E, TWh)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>~55-65</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>~35-45</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>~25-30</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>~15-20</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>~5-8</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Operational Capacity (GW)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>~7-8</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>~5-6</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>~3.5-4.5</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>~2-3</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>~1-1.5</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Data Centre PUE</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>~1.15-1.20</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>~1.12-1.18</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>~1.10</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>~1.10-1.15</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>~1.20-1.30</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>~1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Renewable Energy Coverage</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>100% target</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>100% by 2025</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>100% match</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100% match</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>100% target</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>~50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ENERGY COST ESTIMATES</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Est. Avg Blended Elec. Rate (¢/kWh)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>6-9</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>5-8</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>7-10</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>8-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Est. Annual Energy Cost ($B)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>$3.5-5.0B</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>$2.5-4.0B</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>$1.5-2.5B</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>$1.0-1.5B</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>$0.4-0.8B</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Energy Cost as % of Cloud Rev.</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>~2.5-3.5%</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>~2.0-3.0%</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>~2.0-3.5%</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>~2-3%</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Energy Cost as % of Cloud COGS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>~5-8%</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>~5-7%</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>~5-9%</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>~5-8%</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC MIX (est. % of DC capacity)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>US / North America</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>~55-60%</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>~50-55%</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>~45-50%</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>~70%</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>~50%</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>~20-25%</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>~25-30%</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>~25-30%</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>~15%</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>~20%</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Pacific &amp; Other</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>~15-25%</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>~15-25%</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>~20-30%</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>~15%</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>~30%</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ENERGY HEDGING &amp; PPA STRATEGY</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>PPA Portfolio (GW contracted)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>~30+ GW</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>~19.8+ GW</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>~8+ GW</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>~10+ GW</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>~3+ GW</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Nuclear Investments</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>SMR interest</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Three Mile Island restart</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>6 SMR plants (Kairos)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Nuclear PPA (US)</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Nuclear exploration</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Behind-the-Meter Gen.</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Some co-located solar</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Gas + renewables</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Geothermal + solar</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Solar farms</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>% Revenue Hedged via PPA</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>~60-80%</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>~50-70%</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>~70-90%</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>~60-80%</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>~30-50%</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Sources: Company earnings (Q3/Q4 2025), sustainability reports, analyst estimates. Energy consumption figures are estimates based on capacity and utilisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Energy costs as % of revenue are estimated; hyperscalers do not disclose energy costs separately. Blended rates reflect PPA + grid mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>PPA coverage provides a natural hedge: ~60-90% of energy cost is locked in at contracted rates, reducing spot price exposure.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A37:G37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hyperscaler Margin Impact: Energy Cost Sensitivity by Oil Price Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Operating margin impact (basis points) from energy cost changes under different oil price scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Model Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Cloud Revenue ($B, 2025E annualised)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>N/A (use $160B total rev)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Operating Margin (baseline)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>43.0%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>23.7%</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>~35% (overall)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Est. Energy Cost ($B, baseline)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Energy as % of Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0.75% (of total)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>US DC Capacity Share</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>EU DC Capacity Share</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>RoW DC Capacity Share</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>PPA Hedge Coverage (% energy)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Unhedged Exposure (% energy at spot)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>US Operations: Margin Impact by Oil Price Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Oil Price Scenario</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>US Elec. Rate (¢/kWh)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Rate Change vs Base</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>AWS Margin Impact</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Azure Margin Impact</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>GCP Margin Impact</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Meta Margin Impact</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Oracle Margin Impact</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>S1: Low Oil ($50/bbl)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+23 bps (+0.23pp)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>+20 bps (+0.20pp)</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>+7 bps (+0.07pp)</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>+5 bps (+0.05pp)</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>+28 bps (+0.28pp)</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>S2: Base Case ($70/bbl)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>S3: Moderate High ($90/bbl)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>-18 bps (-0.18pp)</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>-15 bps (-0.15pp)</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>-5 bps (-0.05pp)</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>-4 bps (-0.04pp)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>-21 bps (-0.21pp)</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>S4: High ($110/bbl)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>+26%</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>-46 bps (-0.46pp)</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>-39 bps (-0.39pp)</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>-14 bps (-0.14pp)</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>-10 bps (-0.10pp)</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>-56 bps (-0.56pp)</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>S5: Crisis ($130/bbl)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>+45%</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>-80 bps (-0.80pp)</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>-68 bps (-0.68pp)</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>-24 bps (-0.24pp)</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>-17 bps (-0.17pp)</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>-97 bps (-0.97pp)</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>S6: Extreme ($150/bbl)</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>+63%</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>-112 bps (-1.12pp)</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>-96 bps (-0.96pp)</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>-34 bps (-0.34pp)</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>-24 bps (-0.24pp)</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>-136 bps (-1.36pp)</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>EU Operations: Margin Impact by Oil Price Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Oil Price Scenario</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>EU Elec. Rate (¢/kWh)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Rate Change vs Base</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>AWS Margin Impact</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Azure Margin Impact</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>GCP Margin Impact</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Meta Margin Impact</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Oracle Margin Impact</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>S1: Low Oil ($50/bbl)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>16-18</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>-18 to -23%</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>+18 bps (+0.18pp)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>+25 bps (+0.25pp)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>+7 bps (+0.07pp)</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>+3 bps (+0.03pp)</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>+16 bps (+0.16pp)</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>S2: Base Case ($70/bbl)</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>20-22</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>0 bps</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>S3: Moderate High ($90/bbl)</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>24-27</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>+15 to +27%</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>-24 bps (-0.24pp)</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>-33 bps (-0.33pp)</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>-10 bps (-0.10pp)</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>-4 bps (-0.04pp)</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>-22 bps (-0.22pp)</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>S4: High ($110/bbl)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>30-35</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>+45 to +68%</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>-59 bps (-0.59pp)</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>-81 bps (-0.81pp)</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>-24 bps (-0.24pp)</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>-10 bps (-0.10pp)</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>-54 bps (-0.54pp)</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>S5: Crisis ($130/bbl)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>40-50</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>+90 to +140%</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>-112 bps (-1.12pp)</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>-153 bps (-1.53pp)</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>-45 bps (-0.45pp)</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>-19 bps (-0.19pp)</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>-103 bps (-1.03pp)</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>S6: Extreme ($150/bbl)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>50-60</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>+140 to +190%</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>-168 bps (-1.68pp)</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>-230 bps (-2.30pp)</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>-68 bps (-0.68pp)</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>-29 bps (-0.29pp)</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>-154 bps (-1.54pp)</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Combined Global Margin Impact (US + EU + RoW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Oil Price Scenario</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Brent ($/bbl)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>AWS Op Margin</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Azure Op Margin</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>GCP Op Margin</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Op Margin</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Oracle Op Margin</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>S1: Low Oil ($50/bbl)</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>37.5% (+50 bps)</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>43.6% (+55 bps)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>24.0% (+20 bps)</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>35.1% (+10 bps)</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>25.5% (+55 bps)</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>S2: Base Case ($70/bbl)</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>43.0%</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>23.7%</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>S3: Moderate High ($90/bbl)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C38" s="10" t="inlineStr"/>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>36.5% (-55 bps)</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>42.4% (-60 bps)</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>23.5% (-20 bps)</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>34.9% (-10 bps)</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>24.4% (-55 bps)</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>S4: High ($110/bbl)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="C39" s="11" t="inlineStr"/>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>35.8% (-120 bps)</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>41.6% (-140 bps)</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>23.3% (-45 bps)</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>34.8% (-25 bps)</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>23.7% (-130 bps)</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>S5: Crisis ($130/bbl)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C40" s="11" t="inlineStr"/>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>34.7% (-230 bps)</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>40.5% (-255 bps)</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>22.9% (-85 bps)</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>34.6% (-45 bps)</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>22.4% (-260 bps)</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>S6: Extreme ($150/bbl)</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="C41" s="11" t="inlineStr"/>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>33.6% (-340 bps)</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>39.4% (-365 bps)</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>22.5% (-125 bps)</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>34.4% (-65 bps)</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>21.1% (-390 bps)</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Model: ΔMargin = (ΔElectricity Rate × Unhedged Energy Volume) / Revenue. PPA-hedged portion assumed fixed at contracted rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>EU margin sensitivity ~2x US due to: (1) higher base rates, (2) greater gas dependency in merit order, (3) carbon cost overlay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Google Cloud least exposed due to highest PPA coverage (~80%) and best PUE (~1.10). Oracle most exposed due to lowest PPA hedge (~40%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Meta included for comparison but margin impact is relative to total company revenue ($160B), so DC energy is &lt;1% of total revenue.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A16:I16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario Deep Dive: $50 vs $110 vs $150 Oil — P&amp;L Walkthrough</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>AWS — Illustrative Annual P&amp;L Impact ($B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Base ($70 oil)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Low ($50 oil)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>High ($110 oil)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Extreme ($150 oil)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>$142.0B</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>$142.0B</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>$142.0B</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>$142.0B</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Energy Cost (Total)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>$4.2B</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>$3.6B</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>-$0.6B</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>$5.0B</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>+$0.8B</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>$5.9B</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>+$1.7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  US Energy (58%)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>$2.4B</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>$2.1B</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>-$0.3B</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>$2.9B</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>+$0.5B</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>$3.3B</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>+$0.9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EU Energy (22%)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>$0.9B</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>$0.7B</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>-$0.2B</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>$1.3B</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>+$0.4B</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>$1.6B</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>+$0.7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RoW Energy (20%)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>$0.8B</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>$0.8B</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>-$0.1B</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>$0.9B</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>+$0.1B</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>$1.0B</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>+$0.2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Other COGS</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>$48.4B</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>$48.4B</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>$48.4B</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>$48.4B</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>$52.6B</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>$52.0B</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>-$0.6B</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>$53.4B</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>+$0.8B</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>$54.3B</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>+$1.7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>$89.4B</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>$90.0B</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>+$0.6B</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>$88.6B</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>-$0.8B</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>$87.7B</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>-$1.7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>OpEx (SG&amp;A + R&amp;D)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>$36.9B</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>$36.9B</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>$36.9B</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>$36.9B</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>$52.5B</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>$53.1B</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>+$0.6B</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>$51.7B</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>-$0.8B</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>$50.8B</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>-$1.7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Operating Margin</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>37.4%</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>+40 bps</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>-55 bps</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>35.8%</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>-120 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft Azure (Intelligent Cloud) — Illustrative Annual P&amp;L Impact ($B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Base ($70 oil)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Low ($50 oil)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>High ($110 oil)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Extreme ($150 oil)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>$131.0B</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>$131.0B</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>$131.0B</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>$131.0B</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Energy Cost (Total)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>$3.2B</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>$2.7B</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>-$0.5B</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>$3.9B</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>+$0.7B</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>$4.7B</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>+$1.5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  US Energy (52%)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>$1.7B</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>$1.4B</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>-$0.3B</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>$2.0B</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$0.3B</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>$2.3B</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>+$0.6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EU Energy (28%)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>$0.9B</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>$0.7B</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>-$0.2B</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>$1.3B</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>+$0.4B</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>$1.7B</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>+$0.8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RoW Energy (20%)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>$0.6B</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>$0.6B</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>-$0.1B</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>$0.7B</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>+$0.1B</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>$0.7B</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>+$0.1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Other COGS</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>$41.4B</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>$41.4B</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>$41.4B</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>$41.4B</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>$44.6B</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>$44.1B</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>-$0.5B</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>$45.3B</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>+$0.7B</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>$46.1B</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>+$1.5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>$86.4B</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>$86.9B</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>+$0.5B</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>$85.7B</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>-$0.7B</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>$84.9B</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>-$1.5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>OpEx (SG&amp;A + R&amp;D)</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>$30.1B</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>$30.1B</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>$30.1B</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>$30.1B</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>$56.3B</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>$56.8B</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>+$0.5B</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>$55.6B</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>-$0.7B</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>$54.8B</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>-$1.5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Operating Margin</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>43.0%</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>43.4%</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>+40 bps</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>42.5%</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>-50 bps</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>41.8%</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>-115 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Google Cloud — Illustrative Annual P&amp;L Impact ($B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Base ($70 oil)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Low ($50 oil)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>High ($110 oil)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Extreme ($150 oil)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Δ vs Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>$71.0B</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>$71.0B</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>$71.0B</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>$71.0B</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Energy Cost (Total)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>$2.0B</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>$1.8B</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>-$0.2B</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>$2.3B</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+$0.3B</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>$2.6B</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>+$0.6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  US Energy (48%)</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>$1.0B</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>$0.9B</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>-$0.1B</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>$1.1B</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>+$0.1B</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>$1.2B</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>+$0.2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EU Energy (27%)</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>$0.5B</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>$0.4B</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>-$0.1B</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>$0.7B</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>+$0.2B</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>$0.8B</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>+$0.3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RoW Energy (25%)</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>$0.5B</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>$0.5B</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>$0.0B</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>$0.5B</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>+$0.1B</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>$0.6B</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>+$0.1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Other COGS</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>$32.2B</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>$32.2B</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>$32.2B</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>$32.2B</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>$34.2B</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>$34.0B</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>-$0.2B</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>$34.5B</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>+$0.3B</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>$34.8B</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>+$0.6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>$36.8B</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>$37.0B</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>+$0.2B</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>$36.5B</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>-$0.3B</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>$36.2B</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>-$0.6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>OpEx (SG&amp;A + R&amp;D)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>$20.0B</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>$20.0B</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>$20.0B</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>$20.0B</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>$16.8B</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>$17.0B</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>+$0.2B</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>$16.5B</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>-$0.3B</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>$16.2B</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>-$0.6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Operating Margin</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>23.7%</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>23.9%</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>+25 bps</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>-40 bps</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>22.8%</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>-85 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Illustrative model. Assumes revenue constant across scenarios (no price pass-through to customers in short run).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Energy cost changes reflect oil→gas→electricity pass-through with PPA hedge dampening. EU portion shows higher sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>In practice, hyperscalers can partially offset via: (1) price increases (lagged), (2) shifting workloads to cheaper regions, (3) efficiency gains.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Key Sensitivities &amp; Strategic Takeaways</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Margin Sensitivity Summary (bps impact per $10/bbl oil price increase)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>US Margin Sensitivity
+(bps / $10 oil)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EU Margin Sensitivity
+(bps / $10 oil)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Global Blended
+(bps / $10 oil)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Relative Vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>-8 to -12 bps</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-12 to -20 bps</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>-15 to -18 bps</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>-7 to -10 bps</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>-15 to -25 bps</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>-15 to -20 bps</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Medium-High (EU heavy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>-3 to -5 bps</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-5 to -8 bps</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>-5 to -8 bps</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Low (best hedged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>-2 to -3 bps</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-2 to -3 bps</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>-3 to -4 bps</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Low (energy &lt; 1% of rev)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>-10 to -14 bps</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-10 to -16 bps</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>-15 to -22 bps</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>High (least hedged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Key Takeaways</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Energy is material but not dominant</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>At 2-4% of cloud revenue, energy costs are significant but not the primary margin driver. Even extreme oil scenarios ($150/bbl) compress margins by only 85-390 bps.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>EU operations are the margin vulnerability</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>EU electricity rates are ~2.5x US levels and show ~2x sensitivity to oil/gas price swings. Azure (28% EU capacity) and AWS (22% EU) most exposed.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>GCP (best PUE + PPAs)</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Azure (highest EU share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>PPA hedging is the key differentiator</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Google's ~80% PPA coverage reduces spot exposure to ~20% of energy cost, vs Oracle's 60% spot exposure. This creates 2-3x margin protection difference.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Oil at $110+ is when it starts to matter</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Below $90/bbl, margin impact is &lt;60 bps for all vendors (manageable). At $110+, it becomes a headwind worth ~120-140 bps for AWS/Azure. At $130+, it's a meaningful drag.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Low-oil scenarios</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>EU-heavy operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Price pass-through is the ultimate offset</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Hyperscalers have demonstrated pricing power. A 1-2% price increase on cloud services would more than offset even the extreme energy cost scenario for all vendors.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>All hyperscalers</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Cloud customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>US remains the structurally advantaged market</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>45-55% cheaper electricity, lower gas price volatility, no carbon tax, and more flexible grid access make US the preferred DC investment destination under all scenarios.</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>US-heavy operators</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>EU-only operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Nordics are Europe's safe harbour</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>At ~10¢/kWh (vs 23-28¢ in Germany/Ireland), Nordic markets offer US-comparable energy costs with free cooling benefits. Expect capacity shift to Nordics.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Nordic DC operators</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Frankfurt/Dublin operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Nuclear PPAs are the long-term hedge</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Google (Kairos SMRs), Microsoft (Three Mile Island), and Amazon (SMR interest) are locking in 20+ year nuclear PPAs to structurally de-risk energy costs.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Early nuclear movers</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Late adopters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>AI workloads amplify the energy cost gap</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>GPU-dense AI racks (30-70 kW) consume 4-9x more power per rack. As AI share of workload grows, energy cost sensitivity increases proportionally.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Efficient operators (GCP)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>High-density, unhedged operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Low oil ($50) is a margin tailwind worth 20-55 bps</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>In a recessionary / demand-destruction scenario where oil falls to $50, hyperscalers gain 20-55 bps of margin — a modest but welcome buffer if cloud growth also slows.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>All hyperscalers</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Analysis assumes static revenue (no pass-through pricing). In practice, hyperscalers would adjust pricing within 6-12 months of sustained cost increases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>PPA coverage estimates are based on publicly disclosed renewable energy contracts relative to total consumption. Actual financial hedging may differ.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002F5496"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -983,7 +6860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004472C4"/>
@@ -1768,7 +7645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -2281,7 +8158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -3218,915 +9095,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00BF8F00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Strategic Implications: Energy Costs &amp; Data Centre Investment</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Theme</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>US Implications</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Europe Implications</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr"/>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>LOCATION ECONOMICS</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Energy Cost Arbitrage</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>US industrial rates are 45-55% cheaper than EU average</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Strong pull for new DC investment; Virginia, Texas, Ohio dominate</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Risk of investment leakage to US; Nordics are the EU bright spot</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Intra-Regional Variation</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>5-10x price range within each region</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Oregon/Texas cheapest; California premium market</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Nordics cheapest; Ireland/Germany most expensive despite DC density</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Grid Availability</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Power access becoming binding constraint</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Some delays in Virginia; Texas grid more flexible</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>7-10 year grid connection waits in legacy hubs; Dublin/Amsterdam moratoriums</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>DEMAND &amp; CONSUMPTION</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>AI-Driven Demand Surge</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>US DC demand forecast to double by 2030 (366→728 TWh)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Strongest 4-year electricity demand growth since 2000</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>150% EU DC demand growth expected 2024-2035</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Data Centres as % of Grid</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>US: ~9% of total; Dublin: ~80% of local demand</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Utilities investing heavily to serve DC load</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Grid saturation in key hubs forcing diversification</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Rack Density Escalation</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Average &lt;8 kW moving toward 30+ kW for AI racks</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Higher energy intensity per sqft amplifies cost differences</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Same trend, but with higher base electricity costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>COST MANAGEMENT STRATEGIES</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>PPA Adoption</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Corporates locking in long-term renewable contracts</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Solar PPAs rising +9% Y/Y due to demand; wind competitive in ERCOT</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>EU solar PPAs declining; Spain at €32.50/MWh is highly competitive</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>On-Site Generation</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Operators investing in behind-the-meter power</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Natural gas + solar co-generation; some nuclear SMR interest</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Wind/solar + battery; less gas flexibility due to carbon costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Efficiency Improvements</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>PUE stagnant at ~1.55 globally; hyperscalers at 1.10-1.20</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Marginal gains from liquid cooling for AI workloads</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Nordics benefit from free cooling; reduces PUE to &lt;1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>INVESTMENT OUTLOOK</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Capital Flows</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>$3T infrastructure supercycle through 2030</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>US attracting disproportionate share due to energy + policy advantages</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>€86B foreign investment 2016-2024; but growth slowing vs US</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Hyperscaler Strategy</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Big Tech driving 50% of DC capex</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Concentrating in US; aggressive PPA + nuclear deals</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Expanding in Nordics/Spain; constrained in legacy hubs</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Sovereign Considerations</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Data sovereignty rules keep some workloads local</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Less of a factor domestically; drives some EU-to-US shift</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>GDPR + data localisation rules protect EU DC demand floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Emerging Market Competition</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Middle East, SE Asia offering cheap power + incentives</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>US still preferred for latency and connectivity</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>EU faces competition from Gulf states for non-latency-sensitive loads</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr"/>
-      <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>KEY RISKS</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>US Energy Price Risk</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>AI-driven demand pushing US prices to record highs (17.14¢ all-sector avg early 2026)</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Energy cost advantage may narrow if demand outpaces supply</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Could reduce the US-EU gap if US prices rise faster</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>EU Competitiveness Risk</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>EU wholesale prices ~2x US; carbon costs add €5-10/MWh</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Could accelerate US DC investment at EU's expense</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Need grid investment + renewable buildout to compete</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Carbon Regulation</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>EU ETS at €70/t CO₂; US has no comparable federal scheme</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Regulatory advantage for US operators; lower compliance costs</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Adds ~€5-10/MWh to EU electricity costs for fossil generation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Analysis based on EIA, IEA, Eurostat, Uptime Institute, JLL, Dell'Oro, and LevelTen data as of Q4 2025 / early 2026.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A31:D31"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00808080"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data Sources &amp; Methodology</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Data Used</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>US Energy Information Administration (EIA)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>US retail &amp; wholesale electricity prices by sector and state</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2020-2025, monthly/annual</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EIA Electric Power Monthly</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Industrial, commercial, residential rates; state-level breakdowns</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2020-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>EIA Wholesale Markets Portal</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Day-ahead and real-time hub prices (PJM, ERCOT, etc.)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2020-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Eurostat</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>EU industrial electricity prices by country, incl. taxes &amp; levies</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2023-2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>IEA Electricity 2026 Report</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>EU wholesale prices, demand forecasts, industrial comparisons</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2024-2025 + forecasts</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>IEA Electricity Mid-Year Update 2025</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>H1 2025 wholesale prices by country, year-on-year changes</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>H1 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Ember Climate / Ember Energy</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>European wholesale day-ahead prices, renewables share data</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>2020-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>CubeConsults</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>European industrial electricity price rankings by country (2024)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>LevelTen Energy PPA Price Index</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Solar &amp; wind PPA prices for North America and Europe (Q4 2025)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Uptime Institute Global DC Survey</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>PUE trends, rack densities, sustainability metrics</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2024-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Lawrence Berkeley National Lab (LBNL)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>US data centre energy consumption analysis</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>JLL 2026 Global Data Center Outlook</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>DC market capacity, investment cycles, infrastructure supercycle</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2024-2030 forecasts</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Dell'Oro Group</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Data centre capex forecasts, GPU share of spending</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2024-2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Arizton Advisory</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Global DC market investment sizing</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2023-2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>US data centres and energy outlook</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2025-2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Reuters / Financial Media</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>DC demand-driven electricity price records, policy developments</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>METHODOLOGY NOTES</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Currency Conversion</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>EUR/USD at ~1.09 (2024-2025 average) used for cross-region comparisons</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Energy Cost Scenarios</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Annual cost = IT Load (MW) × PUE × 8,760 hrs × Rate ($/kWh)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Wholesale vs Retail</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>DCs negotiate rates between wholesale and retail; shown separately</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>PPA Impact</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>PPAs can reduce effective rates 10-30% vs retail; growing in adoption</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Data Vintage</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Most data as of Q4 2025 or early 2026; some 2025 figures are estimates</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>